--- a/data/trans_orig/IP04D$aparatos-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$aparatos-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57708</t>
+          <t>57630</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71965</t>
+          <t>71712</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54401</t>
+          <t>54104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68605</t>
+          <t>68547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116813</t>
+          <t>116014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136485</t>
+          <t>136578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,49%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>20657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34661</t>
+          <t>34739</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17587</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31791</t>
+          <t>32088</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42076</t>
+          <t>41983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>61748</t>
+          <t>62547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>290947</t>
+          <t>290296</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>323111</t>
+          <t>322792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>299626</t>
+          <t>300126</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>336343</t>
+          <t>334241</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601147</t>
+          <t>599859</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>648415</t>
+          <t>648570</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,83%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>126000</t>
+          <t>126319</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158164</t>
+          <t>158815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>156820</t>
+          <t>158922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>193537</t>
+          <t>193037</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>293860</t>
+          <t>293705</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>341128</t>
+          <t>342416</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72201</t>
+          <t>72461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94493</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73667</t>
+          <t>73964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95845</t>
+          <t>95613</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153254</t>
+          <t>153615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183288</t>
+          <t>183829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72319</t>
+          <t>71812</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94611</t>
+          <t>94351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76383</t>
+          <t>76615</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98561</t>
+          <t>98264</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155753</t>
+          <t>155212</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185787</t>
+          <t>185426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,69%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>435016</t>
+          <t>433746</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>476483</t>
+          <t>477138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>443984</t>
+          <t>440462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>486528</t>
+          <t>485270</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>890115</t>
+          <t>890850</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>950466</t>
+          <t>951220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231809</t>
+          <t>231154</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273276</t>
+          <t>274546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>265056</t>
+          <t>266314</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>307600</t>
+          <t>311122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>509410</t>
+          <t>508656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569761</t>
+          <t>569026</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31450</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43115</t>
+          <t>43327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38154</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51705</t>
+          <t>50868</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72416</t>
+          <t>73484</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91691</t>
+          <t>91723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27300</t>
+          <t>27391</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16909</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29995</t>
+          <t>30460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35673</t>
+          <t>35641</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54948</t>
+          <t>53880</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>238913</t>
+          <t>239169</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>273655</t>
+          <t>272899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>247999</t>
+          <t>247511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>284652</t>
+          <t>284721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>498495</t>
+          <t>497144</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>548321</t>
+          <t>547270</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,19%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197138</t>
+          <t>197894</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>231880</t>
+          <t>231624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>201435</t>
+          <t>201366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238088</t>
+          <t>238576</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>408559</t>
+          <t>409610</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>458385</t>
+          <t>459736</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,05%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58715</t>
+          <t>57872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80150</t>
+          <t>80012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67224</t>
+          <t>68082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90230</t>
+          <t>90106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134309</t>
+          <t>133177</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164879</t>
+          <t>163315</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90488</t>
+          <t>90626</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>111923</t>
+          <t>112766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95080</t>
+          <t>95204</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118086</t>
+          <t>117228</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>191068</t>
+          <t>192632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>221638</t>
+          <t>222770</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,59%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>341465</t>
+          <t>340584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>382945</t>
+          <t>383439</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>367598</t>
+          <t>366690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>413510</t>
+          <t>411755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>720906</t>
+          <t>722137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>781491</t>
+          <t>784270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>317236</t>
+          <t>316742</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358716</t>
+          <t>359597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>326501</t>
+          <t>328256</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>372413</t>
+          <t>373321</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>658701</t>
+          <t>655922</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>719286</t>
+          <t>718055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23259</t>
+          <t>24310</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42661</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33903</t>
+          <t>33646</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48103</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60610</t>
+          <t>63123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86083</t>
+          <t>86274</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>11619</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31419</t>
+          <t>30368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,46%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28101</t>
+          <t>28358</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30599</t>
+          <t>30408</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56072</t>
+          <t>53559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>294884</t>
+          <t>296279</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>344960</t>
+          <t>345131</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>297744</t>
+          <t>298532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>351486</t>
+          <t>350980</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>610282</t>
+          <t>609062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>678432</t>
+          <t>679815</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,62%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>115550</t>
+          <t>115379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>165626</t>
+          <t>164231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164426</t>
+          <t>164932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>218168</t>
+          <t>217380</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>297990</t>
+          <t>296607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>366140</t>
+          <t>367360</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54584</t>
+          <t>55015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74924</t>
+          <t>75246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64624</t>
+          <t>63431</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87476</t>
+          <t>89135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125939</t>
+          <t>125621</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156301</t>
+          <t>156603</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,32%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73628</t>
+          <t>73306</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93968</t>
+          <t>93537</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94929</t>
+          <t>93270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117781</t>
+          <t>118974</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174656</t>
+          <t>174354</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>205018</t>
+          <t>205336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,04%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>390256</t>
+          <t>391276</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>448835</t>
+          <t>452561</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>413919</t>
+          <t>411370</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>476641</t>
+          <t>473302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>819712</t>
+          <t>821839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>907012</t>
+          <t>904194</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,49%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214904</t>
+          <t>211178</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>273483</t>
+          <t>272463</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>283681</t>
+          <t>287020</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>346403</t>
+          <t>348952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>517048</t>
+          <t>519866</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>604348</t>
+          <t>602221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$aparatos-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$aparatos-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>61789</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54395</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>68184</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>71,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>63,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>79,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>65219</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>57630</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71712</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>57773</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>72014</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>70,61%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>62,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>77,64%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>61789</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>54104</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>68547</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>71,69%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116014</t>
+          <t>117151</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>136578</t>
+          <t>137027</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,74%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24403</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18008</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31797</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>27150</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20657</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34739</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>20355</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>34596</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>29,39%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,36%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>37,61%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24403</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17645</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32088</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>28,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41983</t>
+          <t>41534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62547</t>
+          <t>61410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>92369</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>317955</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>299470</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>334425</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>64,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>60,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>67,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>307175</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>290296</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>322792</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>290086</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>321873</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>68,4%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>64,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>71,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>317955</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>300126</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>334241</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>64,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>599859</t>
+          <t>602319</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>648570</t>
+          <t>647640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,73%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>175208</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>158738</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>193693</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>35,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>32,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>39,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>141936</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>126319</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>158815</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>127238</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>159025</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>31,6%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>175208</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>158922</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>193037</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>35,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>293705</t>
+          <t>294635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>342416</t>
+          <t>339956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>36,08%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>493163</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>493163</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>493163</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449111</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449111</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449111</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>706</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>493163</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>493163</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>493163</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>84917</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74319</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>95931</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>83554</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>72461</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>95000</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>73295</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>94296</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>50,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>56,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>84917</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>73964</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>95613</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>49,31%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153615</t>
+          <t>153633</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>183829</t>
+          <t>184853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>87311</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>76297</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>97909</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>56,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>83258</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>71812</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>94351</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>72516</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>93517</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>49,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>43,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>56,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>87311</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>76615</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>98264</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,69%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155212</t>
+          <t>154188</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185426</t>
+          <t>185408</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>172228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>464662</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>445037</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>486782</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>61,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>59,21%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>660</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>455948</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>433746</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>477138</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>436076</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>477724</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>64,37%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>61,24%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>67,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>464662</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>440462</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>485270</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>61,82%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>890850</t>
+          <t>891042</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>951220</t>
+          <t>952337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,23%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>286922</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>264802</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>306547</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>38,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>35,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>40,79%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>361</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>252344</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>231154</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>274546</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>230568</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>272216</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>35,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>32,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,76%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>286922</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>266314</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>311122</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>38,18%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>508656</t>
+          <t>507539</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569026</t>
+          <t>568834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>751584</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>751584</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>751584</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1021</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>708292</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>751584</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>751584</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>751584</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,72 +2325,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>45147</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38200</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>51894</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>55,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>75,63%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>37144</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31359</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43327</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>30699</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>42926</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>63,22%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>73,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>45147</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>38154</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>50868</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,8%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73484</t>
+          <t>72892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91723</t>
+          <t>90429</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -2443,67 +2443,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>23467</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16720</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>30414</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,2%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24,37%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>44,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>21606</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15423</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27391</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15824</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28051</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>36,78%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>26,25%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23467</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>17746</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>30460</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,2%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35641</t>
+          <t>36935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53880</t>
+          <t>54472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58750</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58750</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58750</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>266209</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>248917</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>286166</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>54,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>51,21%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>58,87%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>382</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>255837</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>239169</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>272899</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>240049</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>274297</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>54,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>50,8%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>57,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>266209</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>247511</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>284721</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>54,77%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>497144</t>
+          <t>495989</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>547270</t>
+          <t>544452</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>219878</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>199921</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>237170</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>45,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>41,13%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>48,79%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>214956</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>197894</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>231624</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>196496</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>230744</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>45,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>42,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>49,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>219878</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>201366</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>238576</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>45,23%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>409610</t>
+          <t>412428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>459736</t>
+          <t>460891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>486087</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>486087</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>486087</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>470793</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>470793</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>470793</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>486087</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>486087</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>486087</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>79145</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>68167</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>90088</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>36,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>69358</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>57872</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>80012</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>58951</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>80839</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>40,65%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>79145</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>68082</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>90106</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>42,71%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133177</t>
+          <t>134224</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163315</t>
+          <t>163519</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,94%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>106165</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>95222</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>117143</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>57,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>51,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>63,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>101280</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>90626</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>112766</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>89799</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>111687</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>59,35%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>53,11%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>66,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>106165</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>95204</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>117228</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>57,29%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>192632</t>
+          <t>192428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>222770</t>
+          <t>221723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,29%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>185310</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>185310</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>185310</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>170638</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>170638</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>170638</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>185310</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>185310</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>185310</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>390501</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>367827</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>410849</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>52,77%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>49,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>55,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>362339</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>340584</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>383439</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>340992</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>383063</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>51,75%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>48,64%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>54,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>390501</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>366690</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>411755</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>722137</t>
+          <t>722197</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>784270</t>
+          <t>783510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>349510</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>329162</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>372184</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>47,23%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>50,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>517</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>337842</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>316742</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>359597</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>317118</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>359189</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>48,25%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>45,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51,36%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>349510</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>328256</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>373321</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>655922</t>
+          <t>656682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>718055</t>
+          <t>717995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,85%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>700181</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,72 +3928,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37993</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31039</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>43883</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>66,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>54,71%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>77,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>35226</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24310</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43059</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64,42%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>41256</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33646</t>
+          <t>28999</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47675</t>
+          <t>38705</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>76482</t>
+          <t>72225</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63123</t>
+          <t>62413</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86274</t>
+          <t>79365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18739</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>25693</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>45,29%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>19452</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11619</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30368</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>35,58%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,25%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>55,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20748</t>
+          <t>12527</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14329</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>40200</t>
+          <t>31265</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30408</t>
+          <t>24125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53559</t>
+          <t>41077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>39,69%</t>
         </is>
       </c>
     </row>
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>309658</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>284538</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>328397</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>65,18%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,89%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>69,13%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>431</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>315522</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>296279</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>345131</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>68,52%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>64,34%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>74,95%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>328236</t>
+          <t>291825</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>298532</t>
+          <t>276652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>350980</t>
+          <t>308780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>643758</t>
+          <t>601483</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>609062</t>
+          <t>572057</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>679815</t>
+          <t>626645</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>165404</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>146665</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>190524</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>34,82%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>30,87%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,11%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>144988</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>115379</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>164231</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31,48%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>187676</t>
+          <t>140623</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164932</t>
+          <t>123668</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>217380</t>
+          <t>155796</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>332664</t>
+          <t>306027</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296607</t>
+          <t>280865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>367360</t>
+          <t>335453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475062</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>655</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>515912</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>976422</t>
+          <t>907510</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976422</t>
+          <t>907510</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>976422</t>
+          <t>907510</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4614,72 +4614,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>72494</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>62146</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>83597</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>43,29%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>37,11%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>49,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>65159</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>55015</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75246</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>43,86%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>37,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50,65%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>76197</t>
+          <t>66165</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63431</t>
+          <t>56065</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89135</t>
+          <t>75710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>141355</t>
+          <t>138658</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125621</t>
+          <t>125472</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156603</t>
+          <t>154510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>48,84%</t>
         </is>
       </c>
     </row>
@@ -4727,72 +4727,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>94968</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>83865</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>105316</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>56,71%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>50,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>62,89%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>83393</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>73306</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>93537</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>56,14%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>49,35%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>62,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>106208</t>
+          <t>82736</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93270</t>
+          <t>73191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118974</t>
+          <t>92836</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>189602</t>
+          <t>177704</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174354</t>
+          <t>161852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>205336</t>
+          <t>190890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>60,34%</t>
         </is>
       </c>
     </row>
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>148552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>148901</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>330957</t>
+          <t>316362</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>420145</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>393508</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>445390</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>60,08%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>56,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>63,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>589</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>415906</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>391276</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>452561</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>62,66%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>58,95%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>68,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>445689</t>
+          <t>392221</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>411370</t>
+          <t>372021</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>473302</t>
+          <t>412344</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>861595</t>
+          <t>812366</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>821839</t>
+          <t>781551</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>904194</t>
+          <t>847185</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,82%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>279111</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>253866</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>305748</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>39,92%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>36,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>43,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>352</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>247833</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>211178</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>272463</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>37,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>41,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>314633</t>
+          <t>235885</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>287020</t>
+          <t>215762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>348952</t>
+          <t>256085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>562465</t>
+          <t>514996</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>519866</t>
+          <t>480177</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>602221</t>
+          <t>545811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>663739</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628106</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1424060</t>
+          <t>1327362</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1424060</t>
+          <t>1327362</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1424060</t>
+          <t>1327362</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
